--- a/Data-Normalization/Data Example/big data.xlsx
+++ b/Data-Normalization/Data Example/big data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Finance-Project\Prototype2\Example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Finance-Project\Data-Normalization\Data Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEDBF5C-035C-462F-922B-7BBFA8504DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA717A9-6438-472C-9A87-D94492515F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CA62BB2-8104-49F2-BC93-4318D9023633}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{4CA62BB2-8104-49F2-BC93-4318D9023633}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -47,8 +47,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -589,7 +591,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42">
       <alignment vertical="center"/>
@@ -601,6 +603,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1005,11 +1010,11 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>45000</v>
-      </c>
-      <c r="F2">
-        <v>45000</v>
+      <c r="E2" s="5">
+        <v>45000.15</v>
+      </c>
+      <c r="F2" s="5">
+        <v>-45000.15</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75">
@@ -1025,11 +1030,11 @@
       <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3">
-        <v>45000</v>
-      </c>
-      <c r="F3">
-        <v>45000</v>
+      <c r="E3" s="6">
+        <v>45000.15</v>
+      </c>
+      <c r="F3" s="6">
+        <v>-45000.15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75">
@@ -1045,11 +1050,11 @@
       <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E4">
-        <v>45000</v>
-      </c>
-      <c r="F4">
-        <v>45000</v>
+      <c r="E4" s="7">
+        <v>45000.15</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45000.15</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75">
@@ -1063,10 +1068,10 @@
       <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>45000</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="7">
+        <v>45000</v>
+      </c>
+      <c r="F5" s="7">
         <v>45000</v>
       </c>
     </row>

--- a/Data-Normalization/Data Example/big data.xlsx
+++ b/Data-Normalization/Data Example/big data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Finance-Project\Data-Normalization\Data Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA717A9-6438-472C-9A87-D94492515F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDEB382-DC56-4BBD-9E77-55B0986FC04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{4CA62BB2-8104-49F2-BC93-4318D9023633}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="12">
   <si>
     <t>商户</t>
   </si>
@@ -41,6 +41,21 @@
   </si>
   <si>
     <t>Indomaret</t>
+  </si>
+  <si>
+    <t>cafepoint</t>
+  </si>
+  <si>
+    <t>grab bcs</t>
+  </si>
+  <si>
+    <t>bluebirdtaxi</t>
+  </si>
+  <si>
+    <t>iuran bpjs</t>
+  </si>
+  <si>
+    <t>bus angkot</t>
   </si>
 </sst>
 </file>
@@ -1105,6 +1120,9 @@
       <c r="D7" t="s">
         <v>6</v>
       </c>
+      <c r="E7">
+        <v>45000</v>
+      </c>
       <c r="F7">
         <v>45000</v>
       </c>
@@ -1120,9 +1138,12 @@
         <v>45900</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8">
+        <v>45000</v>
+      </c>
+      <c r="F8">
         <v>45000</v>
       </c>
     </row>
@@ -1137,7 +1158,7 @@
         <v>45900</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>45000</v>
@@ -1157,7 +1178,7 @@
         <v>45900</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>45000</v>
@@ -1187,7 +1208,7 @@
         <v>45900</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>45000</v>
@@ -1227,7 +1248,7 @@
         <v>45900</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>45000</v>
